--- a/results_all_data/tab_recap_itemsets_0.95.xlsx
+++ b/results_all_data/tab_recap_itemsets_0.95.xlsx
@@ -419,13 +419,13 @@
         <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>52736</v>
+        <v>52721</v>
       </c>
       <c r="C2" t="n">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="D2" t="n">
-        <v>4.53</v>
+        <v>4.54</v>
       </c>
       <c r="E2" t="n">
         <v>8</v>
@@ -442,19 +442,19 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>86454</v>
+        <v>58727</v>
       </c>
       <c r="C3" t="n">
-        <v>1234</v>
+        <v>1001</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>4.84</v>
       </c>
       <c r="E3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="n">
-        <v>3.43</v>
+        <v>3.45</v>
       </c>
       <c r="G3" t="n">
         <v>5</v>
@@ -465,19 +465,19 @@
         <v>9</v>
       </c>
       <c r="B4" t="n">
-        <v>106625</v>
+        <v>64168</v>
       </c>
       <c r="C4" t="n">
-        <v>1268</v>
+        <v>989</v>
       </c>
       <c r="D4" t="n">
-        <v>5.09</v>
+        <v>4.92</v>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="n">
-        <v>3.46</v>
+        <v>3.43</v>
       </c>
       <c r="G4" t="n">
         <v>5</v>
@@ -488,19 +488,19 @@
         <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>115425</v>
+        <v>64444</v>
       </c>
       <c r="C5" t="n">
-        <v>1921</v>
+        <v>1111</v>
       </c>
       <c r="D5" t="n">
-        <v>5.35</v>
+        <v>4.96</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="n">
-        <v>3.47</v>
+        <v>3.4</v>
       </c>
       <c r="G5" t="n">
         <v>5</v>
@@ -511,19 +511,19 @@
         <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>123116</v>
+        <v>65035</v>
       </c>
       <c r="C6" t="n">
-        <v>1770</v>
+        <v>958</v>
       </c>
       <c r="D6" t="n">
-        <v>5.51</v>
+        <v>5.11</v>
       </c>
       <c r="E6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F6" t="n">
-        <v>3.31</v>
+        <v>3.19</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
@@ -534,7 +534,7 @@
         <v>12</v>
       </c>
       <c r="B7" t="n">
-        <v>2527</v>
+        <v>2520</v>
       </c>
       <c r="C7" t="n">
         <v>59</v>
@@ -557,19 +557,19 @@
         <v>13</v>
       </c>
       <c r="B8" t="n">
-        <v>3936</v>
+        <v>2667</v>
       </c>
       <c r="C8" t="n">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="D8" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="E8" t="n">
         <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="G8" t="n">
         <v>4</v>
@@ -580,19 +580,19 @@
         <v>14</v>
       </c>
       <c r="B9" t="n">
-        <v>3756</v>
+        <v>2389</v>
       </c>
       <c r="C9" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="D9" t="n">
-        <v>2.77</v>
+        <v>2.57</v>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F9" t="n">
-        <v>1.99</v>
+        <v>2.07</v>
       </c>
       <c r="G9" t="n">
         <v>3</v>
@@ -603,19 +603,19 @@
         <v>15</v>
       </c>
       <c r="B10" t="n">
-        <v>4945</v>
+        <v>2864</v>
       </c>
       <c r="C10" t="n">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="D10" t="n">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F10" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="G10" t="n">
         <v>4</v>
@@ -626,19 +626,19 @@
         <v>16</v>
       </c>
       <c r="B11" t="n">
-        <v>4502</v>
+        <v>2659</v>
       </c>
       <c r="C11" t="n">
-        <v>93</v>
+        <v>54</v>
       </c>
       <c r="D11" t="n">
-        <v>2.94</v>
+        <v>2.72</v>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="G11" t="n">
         <v>3</v>
